--- a/registration_forms/036_regional_operator_licensing_registration_form--registration_forms.xlsx
+++ b/registration_forms/036_regional_operator_licensing_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>geo_location</t>
+          <t>geo_location_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>geo location</t>
+          <t>Geo Location 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_person_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>contact person</t>
+          <t>Contact Person 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>geo_location</t>
+          <t>geo_location_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>geo location</t>
+          <t>Geo Location 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>region_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>Region 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>operator_license_type</t>
+          <t>operator_license_type_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>operator license type</t>
+          <t>Operator License Type 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>geo_location</t>
+          <t>geo_location_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>geo location</t>
+          <t>Geo Location 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>region_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>Region 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1262,58 +1262,58 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>geo_location_choices</t>
+          <t>geo_location_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>geo_location_choices</t>
+          <t>geo_location_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>geo_location_choices</t>
+          <t>geo_location_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>operator_license_type_choices</t>
+          <t>operator_license_type_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>operator_license_type_choices</t>
+          <t>operator_license_type_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>operator_license_type_choices</t>
+          <t>operator_license_type_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>operator_license_type_choices</t>
+          <t>operator_license_type_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,51 +1381,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>geo_location_choices</t>
+          <t>geo_location_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>geo_location_choices</t>
+          <t>geo_location_4_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>geo_location_choices</t>
+          <t>geo_location_4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
